--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_02_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_02_21_Cau.xlsx
@@ -813,13 +813,17 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -827,7 +831,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Hosted TCO=4.000+500+1.200=5.700; self-hosted=3.000+600+2.000+500=6.100; chênh lệch=400 USD/tháng.</t>
+          <t>Hosted TCO: $4.000 + $500 + $1.200 = $5.700. Self-hosted TCO: $3.000 + $600 + $2.000 + $500 = $6.100. Chênh lệch TCO self-hosted trừ hosted: $6.100 - $5.700 = 400 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -927,13 +931,17 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>111111</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -941,7 +949,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Điểm hòa vốn TCO: 500 + 0.04*N = 4500 + 0.004*N =&gt; 0.036*N = 4000 =&gt; N = 4000 / 0.036 ≈ 111,111 request/tháng.</t>
+          <t>Break-even volume: 500 + 0,04*N = 4500 + 0,004*N =&gt; 0,036*N = 4000 =&gt; N = 4000 / 0,036 ≈ 111.111 requests/tháng.</t>
         </is>
       </c>
     </row>
@@ -959,7 +967,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -973,7 +985,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính từng option ở cùng volume trước khi trừ.</t>
+          <t>Tại V = 200.000 requests/tháng: Hosted cost = $500 + $0,04 * 200.000 = $500 + $8.000 = $8.500. Self-hosted cost = $4.500 + $0,004 * 200.000 = $4.500 + $800 = $5.300. Self-hosted rẻ hơn hosted: $8.500 - $5.300 = 3.200 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1163,13 +1175,17 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1177,7 +1193,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Per request=$0,002+$0,002=$0,004; 1,5 triệu request/tháng ⇒ $6.000.</t>
+          <t>Mỗi request: 1.000 input tokens * $2/M + 200 output tokens * $10/M = $0,002 + $0,002 = $0,004/request. Hàng tháng có 50.000 * 30 = 1.500.000 requests =&gt; Tổng chi phí: 1.500.000 * $0,004 = 6.000 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1211,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1209,7 +1229,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính input và output subtotal riêng trước khi cộng.</t>
+          <t>Tổng API subtotal: (496 triệu input tokens * $1,5 / triệu) + (186 triệu output tokens * $6 / triệu) = 496 * 1,5 + 186 * 6 = $744 + $1.116 = 1.860 USD/tháng.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_02_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_02_21_Cau.xlsx
@@ -624,10 +624,39 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Constraint cần thành workload và acceptance rule chạy được.
-Phân tích theo nguyên lý thiết kế: Constraint cần thành workload và acceptance rule chạy được.</t>
+- 1.0đ: Đặc tả Acceptance Test 1 kiểm thử khả năng offline 2 giờ kèm cơ chế đồng bộ phục hồi tự động.
+- 1.0đ: Đặc tả Acceptance Test 2 kiểm thử độ trễ CPU-only với ngưỡng P95 &lt; 5 giây cụ thể.
+- 1.0đ: Đặc tả Acceptance Test 3 kiểm thử tranh chấp dữ liệu tồn kho và giải quyết xung đột (conflict resolution).
+- 1.0đ: Nêu rõ kịch bản thử nghiệm chi tiết và tiêu chí đạt chuẩn định lượng cho từng bài test.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Đặc tả Bộ Kiểm thử Chấp nhận (Acceptance Test Suite Specification) cho Triển khai tại Chi nhánh (Branch Office):
+1. **Acceptance Test 1: Kiểm thử Tự chủ Ngoại tuyến Kéo dài (Extended Offline Autonomy Test)**:
+- **Ràng buộc**: Chi nhánh mất kết nối WAN tối đa 2 giờ mỗi ngày.
+- **Kịch bản Thử nghiệm (Test Scenario)**:
+  + Tại thời điểm $T_0$, ngắt kết nối mạng WAN của chi nhánh trong đúng 2 giờ 15 phút.
+  + Thực hiện 500 truy vấn tra cứu kho hàng và tạo 50 đơn hàng mới tại quầy trong thời gian mất mạng.
+- **Tiêu chí Đạt chuẩn (Pass Criteria)**:
+  + Hệ thống ứng dụng chi nhánh vẫn hoạt động 100% trơn tru, không báo lỗi mạng cho nhân viên.
+  + Toàn bộ các giao dịch phát sinh được lưu trữ an toàn trong Local Transaction Journal.
+  + Khi kết nối WAN được khôi phục tại $T + 2h15$, hệ thống tự động đồng bộ hai chiều (Re-sync) về máy chủ trung tâm trong vòng dưới 5 phút mà không làm mất mát dù chỉ 1 bản ghi.
+2. **Acceptance Test 2: Kiểm thử Hiệu năng Suy luận Thuần CPU (CPU-Only Latency Benchmark)**:
+- **Ràng buộc**: Máy chủ chi nhánh chỉ có CPU (không có GPU), thời gian phản hồi tra cứu phải dưới 5 giây.
+- **Kịch bản Thử nghiệm**:
+  + Triển khai mô hình AI (đã qua tối ưu hóa lượng hóa INT8/INT4 qua ONNX Runtime / OpenVINO) trên CPU Intel Xeon 8-cores của chi nhánh.
+  + Gửi 50 truy vấn tra cứu ngữ nghĩa liên tục dưới mức tải nền CPU 70%.
+- **Tiêu chí Đạt chuẩn**:
+  + Thời gian phản hồi phân vị **P95 Latency $\le 3.5$ giây** và **Max Latency $\le 4.8$ giây** (thỏa mãn tuyệt đối yêu cầu $&lt; 5$ giây).
+3. **Acceptance Test 3: Kiểm thử Tính Nhất quán Dữ liệu Tồn kho (Inventory Integrity &amp; Conflict Resolution Test)**:
+- **Ràng buộc**: Sai lệch dữ liệu tồn kho gây mất đơn hàng của khách.
+- **Kịch bản Thử nghiệm**:
+  + Tạo kịch bản tranh chấp: Một mặt hàng chỉ còn đúng 1 sản phẩm cuối cùng. Chi nhánh bán sản phẩm này trong khi đang offline; đồng thời trên web trung tâm cũng có khách đặt mua mặt hàng đó.
+- **Tiêu chí Đạt chuẩn**:
+  + Cơ chế kiểm soát tồn kho áp dụng mô hình khóa phân tán hoặc đặt chỗ tạm thời (Pessimistic Reservation / Distributed Conflict Resolution Policy).
+  + Khi chi nhánh online trở lại, hệ thống đối soát phát hiện xung đột và xử lý theo đúng chính sách ưu tiên nghiệp vụ định trước (ví dụ: ưu tiên đơn tại quầy, bồi thường voucher cho đơn web), bảo đảm số lượng tồn kho trong database không bao giờ bị âm (`inventory_count &gt;= 0`).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đặc tả Kiểm thử Chấp nhận Triển khai Phân tán (Acceptance Tests for Distributed Edge Deployments): Một hệ thống phân tán tại các chi nhánh bán lẻ phải đối mặt với hai kẻ thù lớn: sự đứt gãy mạng diện rộng (Network Partitions) và phần cứng hạn chế (CPU-only). Các bài kiểm thử chấp nhận (Acceptance Tests) phải mô phỏng chính xác các điều kiện khắc nghiệt này để bảo đảm: hệ thống sống sót khi offline 2h, suy luận nhanh trên CPU dưới 5s, và giải quyết tranh chấp tồn kho bảo vệ doanh thu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+CAP Theorem &amp; Martin Kleppmann: Designing Data-Intensive Applications (Chapter 5: Replication &amp; Conflict Resolution)</t>
         </is>
       </c>
     </row>
@@ -706,10 +735,26 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Topology được chọn theo scenario, không theo slogan.
-Phân tích theo nguyên lý thiết kế: Topology được chọn theo scenario, không theo slogan.</t>
+- 1.0đ: Xây dựng bảng quyết định so sánh đầy đủ 3 phương án (Pure Cloud, Pure On-prem, Hybrid) trên các tiêu chí cốt lõi.
+- 1.0đ: Phân tích và loại trừ thuyết phục phương án Pure Cloud do vi phạm quy định Data Residency.
+- 1.0đ: Phân tích và loại trừ thuyết phục phương án Pure On-prem do thời gian mua sắm (12 tuần) vượt quá deadline (4 tuần).
+- 1.0đ: Bảo vệ vững chắc phương án Hybrid Topology dựa trên việc tận dụng gateway có sẵn và thỏa mãn cả hai ràng buộc.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Lập Bảng Quyết định Topology (Enterprise Topology Decision Table) và Lập luận Bảo vệ Lựa chọn Hiện tại:
+1. **Bảng Quyết định Lựa chọn Topology (Topology Decision Table)**:
+| Tiêu chí Doanh nghiệp | Phương án 1: Pure Public Cloud (Đám mây Công cộng Hoàn toàn) | Phương án 2: Pure On-premise (Máy chủ Nội bộ Hoàn toàn) | Phương án 3: Hybrid Topology với Gateway Sẵn có (Đám mây Lai) |
+| :--- | :--- | :--- | :--- |
+| **Tuân thủ Data Residency (Cấm Raw Data ra Cloud)** | **LOẠI BỎ (FAIL)**: Đẩy dữ liệu thô ra cloud vi phạm trực tiếp quy định bảo vệ dữ liệu nội địa. | **ĐẠT (PASS)**: Toàn bộ dữ liệu nằm 100% trong phòng máy nội bộ. | **ĐẠT (PASS)**: Raw data ở on-premise; gateway lọc và chỉ đẩy dữ liệu tổng hợp (aggregate) ra cloud. |
+| **Thời hạn Triển khai (Khắt khe: Launch trong 4 tuần)** | **ĐẠT (PASS)**: Triển khai nhanh trên cloud chỉ mất 1-2 tuần. | **LOẠI BỎ (FAIL)**: Thời gian mua sắm phần cứng on-prem mất tới **12 tuần** (quá hạn 8 tuần). | **ĐẠT (PASS)**: Sử dụng ngay hạ tầng On-premise hiện có kết hợp Hybrid Gateway **đã có sẵn**, kịp launch trong 4 tuần. |
+| **Chi phí Đầu tư Ban đầu (CAPEX)** | Thấp: Trả theo phí sử dụng OPEX. | Rất cao: Phải chi tiền mua máy chủ mới ngay lập tức. | Thấp / Tối ưu: Tận dụng phần cứng cũ và gateway có sẵn. |
+| **Kết luận Đánh giá** | **BỊ PHỦ QUYẾT BỞI LUẬT** | **BỊ PHỦ QUYẾT BỞI DEADLINE** | **LỰA CHỌN TỐI ƯU DUY NHẤT (SELECTED)** |
+2. **Lập luận Bảo vệ Lựa chọn Hiện tại (Hybrid Topology Defense)**:
+- **Tính Bắt buộc của Thực tế (Pragmatic Engineering)**: Lựa chọn Topology trong doanh nghiệp không dựa trên khẩu hiệu lý thuyết ('Cloud-First' hay 'Onprem-Only') mà dựa trên ma trận ràng buộc thực tế.
+- **Tháo gỡ Thế bế tắc Hoàn hảo**: Phương án Pure Cloud bị phủ quyết bởi Luật Data Residency; Phương án Pure On-premise bị phủ quyết bởi Deadline 4 tuần (mua sắm mất 12 tuần). Phương án **Hybrid Topology** là chiếc chìa khóa vàng duy nhất giải quyết trọn vẹn cả hai ràng buộc: giữ raw data an toàn tuyệt đối tại chỗ, tận dụng gateway có sẵn để ra mắt đúng hẹn trong 4 tuần, và tận dụng sức mạnh tính toán đám mây cho các dữ liệu tổng hợp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Lựa chọn Topology trong Kiến trúc Doanh nghiệp (Enterprise Topology Selection Methodology): Các quyết định kiến trúc lớn luôn bị chi phối bởi hai gọng kìm: Ràng buộc Tuân thủ (Compliance Constraints) và Ràng buộc Thời gian/Chi phí (Time-to-Market Constraints). Bảng quyết định (Decision Table) là công cụ minh bạch nhất để loại bỏ các phương án bất khả thi. Lựa chọn Hybrid không phải là sự thỏa hiệp tạm bợ, mà là giải pháp kỹ nghệ tối ưu được chứng minh bằng các sự thật khách quan.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SEI Architecture Tradeoff Analysis Method (ATAM) &amp; AWS/Azure Hybrid Cloud Architecture Frameworks</t>
         </is>
       </c>
     </row>
@@ -792,10 +837,34 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi mũi tên phải mang data class và control.
-Phân tích theo nguyên lý thiết kế: Mỗi mũi tên phải mang data class và control.</t>
+- 1.0đ: Mô tả mạch lạc toàn bộ luồng xử lý qua 4 chặng từ On-prem sang Cloud và quay trở lại.
+- 1.0đ: Thiết lập cơ chế kiểm soát ranh giới nghiêm ngặt tại Ingestion Gateway (loại bỏ PII, chỉ gửi non-sensitive fields).
+- 1.0đ: Thiết lập chốt chặn bắt buộc chuyên gia con người (Reviewer Sign-off) khi có đề xuất từ chối bồi thường (denial).
+- 1.0đ: Xây dựng bảng ma trận truy vết chi tiết từng chặng với cấp độ phân loại dữ liệu và cơ chế kiểm soát tương ứng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Mô tả Luồng Xử lý Hồ sơ Bảo hiểm Lai (Hybrid Claim-Processing Flow) và Truy vết Kiểm soát qua Từng Ranh giới:
+1. **Mô tả Kiến trúc và Luồng Dữ liệu Tuần tự (Step-by-Step Flow Description)**:
+- **Chặng 1 (Tại On-premise Secure Storage)**:
+  + Hồ sơ yêu cầu bồi thường bảo hiểm gốc (`raw_claim_document`: bệnh án, hóa đơn viện phí chứa đầy đủ thông tin cá nhân PII) được tiếp nhận và lưu giữ vĩnh viễn trên máy chủ nội bộ On-premise.
+- **Chặng 2 (Vượt Ranh giới On-prem -&gt; Cloud qua Ingestion Gateway)**:
+  + *Dữ liệu truyền qua*: Chỉ các trường phi nhạy cảm đã được bóc tách (`extracted_non_sensitive_fields`: mã danh mục viện phí, mã chẩn đoán ICD-10, số tiền đề nghị bồi thường, số năm tham gia bảo hiểm) kèm `pseudo_claim_id`.
+  + *Cơ chế kiểm soát ranh giới*: Ingestion Gateway kiểm tra schema nghiêm ngặt: nếu phát hiện bất kỳ trường PII nào (tên, số CMND/CCCD, địa chỉ), gói tin bị DROP ngay lập tức.
+- **Chặng 3 (Xử lý tại Cloud AI Model)**:
+  + Mô hình AI trên Cloud chạy thuật toán đối soát chính sách và chấm điểm rủi ro: đưa ra đề xuất chấp thuận (`APPROVE`) hoặc từ chối (`DENIAL`). Kết quả được gửi ngược về On-premise qua kênh mTLS an toàn.
+- **Chặng 4 (Phân luồng Phê duyệt Nghiệp vụ tại On-premise)**:
+  + Nếu AI đề xuất `APPROVE`: Tự động chuyển tiếp sang hệ thống thanh toán tự động.
+  + Nếu AI đề xuất `DENIAL`: Kích hoạt chốt chặn **Human-in-the-Loop Review Gate**.   Quyết định từ chối bắt buộc phải chuyển tới màn hình của Bác sĩ / Thẩm định viên Bảo hiểm con người (Human Claims Reviewer).   Chuyên gia mở toàn bộ tài liệu gốc on-premise, ký số xác nhận từ chối kèm lý do điều khoản cụ thể.
+2. **Bảng Truy vết Phân loại Dữ liệu và Kiểm soát Ranh giới (Boundary Trace Matrix)**:
+| Chặng Luồng | Nguồn -&gt; Đích | Lớp Dữ liệu (Data Class) | Cơ chế Kiểm soát Bắt buộc (Mandatory Control) |
+| :--- | :--- | :--- | :--- |
+| Chặng 1 | Client -&gt; On-prem Storage | Class 4: Highly Sensitive PII | Mã hóa AES-256 at rest, phân quyền truy cập nội bộ RBAC |
+| Chặng 2 | On-prem -&gt; Cloud Gateway | Class 1: De-identified Features | Mã hóa TLS 1.3 in transit, Gateway Schema Whitelist Filter |
+| Chặng 3 | Cloud -&gt; On-prem Gateway | Class 2: AI Risk Recommendation | Chữ ký số xác thực nguồn gốc model (HMAC Signature) |
+| Chặng 4 | Gateway -&gt; Reviewer Queue | Class 4: Full Case Provenance | Human Reviewer Mandatory Sign-off for Denial decisions |
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Luồng Dữ liệu Xuyên Biên giới (Cross-boundary Data Flow Architecture): Mỗi mũi tên kết nối giữa hai hệ thống phân tán phải mang đầy đủ hai thuộc tính: Lớp Dữ liệu (Data Classification) và Cơ chế Kiểm soát (Security Controls). Trong quy trình xử lý bồi thường bảo hiểm, việc bảo vệ tài liệu thô tại chỗ kết hợp với chốt chặn con người khi từ chối bồi thường vừa đáp ứng quy chuẩn bảo vệ dữ liệu vừa tuân thủ đạo đức kinh doanh bảo hiểm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST SP 800-53: Boundary Protection (SC-7) &amp; NAIC (National Association of Insurance Commissioners) Model Law on AI</t>
         </is>
       </c>
     </row>
@@ -862,10 +931,35 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So cùng kỳ và giữ các cost con người/hidden.
-Phân tích theo nguyên lý thiết kế: So cùng kỳ và giữ các cost con người/hidden.</t>
+- 1.0đ: Tính đúng TCO của Hosted Solution: 10.000 USD/tháng.
+- 1.0đ: Tính đúng đầy đủ TCO của Self-hosted Solution (bao gồm cả nhân sự ops, điện, khấu hao): 12.000 USD/tháng.
+- 1.0đ: Đưa ra so sánh chuẩn xác ở thời điểm hiện tại: Hosted tiết kiệm hơn 2.000 USD/tháng.
+- 1.0đ: Phân tích sâu sắc các giả định chưa đủ để kết luận dài hạn (điểm bão hòa công suất khi scale, chu kỳ lỗi thời phần cứng, downtime SLA).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. So sánh Tổng Chi phí Sở hữu Hàng tháng (Monthly Total Cost of Ownership - TCO Comparison):
+- **Phương án 1: Hosted Solution (Sử dụng API Đám mây)**:
+  + Chi phí gọi API mô hình: $7.000 USD/tháng.
+  + Chi phí lưu trữ (Storage): $1.000 USD/tháng.
+  + Chi phí chuyên gia đánh giá (Review/Labor): $2.000 USD/tháng.
+  + **Tổng TCO Hosted** = $7.000 + 1.000 + 2.000 = \mathbf{10.000 \text{ USD/tháng}}.
+- **Phương án 2: Self-hosted Solution (Tự vận hành Cụm GPU)**:
+  + Khấu hao phần cứng GPU (GPU amortization): $5.000 USD/tháng.
+  + Điện năng và làm mát (Power &amp; Cooling): $1.000 USD/tháng.
+  + Nhân sự vận hành hạ tầng (Ops/DevOps labor): $3.000 USD/tháng.
+  + Chi phí lưu trữ (Storage): $1.000 USD/tháng.
+  + Chi phí chuyên gia đánh giá (Review/Labor): $2.000 USD/tháng.
+  + **Tổng TCO Self-hosted** = $5.000 + 1.000 + 3.000 + 1.000 + 2.000 = \mathbf{12.000 \text{ USD/tháng}}.
+- **Kết luận Ngắn hạn Hiện tại**: Phương án **Hosted rẻ hơn $2.000 USD/tháng** (tiết kiệm 16.7% chi phí) so với Self-hosted.
+2. Các Giả định Chưa đủ để Kết luận Dài hạn (Flawed Long-term Assumptions):
+- **Giả định Hiệu suất Cố định 60% (Utilization Scalability Assumption)**: Chi phí Self-hosted đang tính trên giả định GPU chạy ở mức 60% công suất. Nếu lưu lượng doanh nghiệp tăng trưởng gấp 2 hoặc gấp 3 lần trong tương lai:
+  + Chi phí Hosted API sẽ **tăng vọt tuyến tính** lên $14.000 hoặc $21.000 USD/tháng.
+  + Trong khi chi phí Self-hosted phần cứng ($5.000 khấu hao + $3.000 ops) là **chi phí cố định (Fixed Cost)**, có thể gánh tới 90% công suất mà không phát sinh thêm tiền mua GPU,   khiến điểm cân bằng chi phí (Break-even Point) sẽ đảo chiều nghiêng hẳn về Self-hosted.
+- **Bỏ sót Chi phí Vòng đời Phần cứng (Hardware Lifecycle &amp; Obsolescence Risk)**: Sau 2-3 năm, phần cứng GPU sẽ bị lỗi thời trước các kiến trúc model mới; Self-hosted sẽ đòi hỏi khoản tái đầu tư CAPEX khổng lồ.
+- **Chưa tính Chi phí Cơ hội &amp; Downtime SLA**: Hosted API có SLA 99.9% từ nhà cung cấp lớn; Self-hosted đòi hỏi đội Ops tự trực đêm, nếu sập cụm GPU chi phí gián đoạn kinh doanh có thể vượt xa $2.000 USD tiết kiệm được.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân tích Tổng Chi phí Sở hữu trong AI (TCO Analysis: Hosted API vs Self-hosted GPU): Một sai lầm kinh điển khi so sánh TCO là chỉ nhìn vào chi phí mua GPU so với tiền hóa đơn API, hoàn toàn quên mất các 'chi phí ẩn' khổng lồ: tiền điện, tiền nhân sự DevOps trực hạ tầng, và chi phí rà soát con người. Hơn nữa, kết luận ngắn hạn ($10k vs $12k) không thể áp dụng cho dài hạn nếu không mô hình hóa sự biến động của lưu lượng (Scale Sensitivity) và chu kỳ khấu hao phần cứng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation: Cloud TCO &amp; Unit Economics &amp; Andreessen Horowitz: Navigating the High Cost of AI Compute</t>
         </is>
       </c>
     </row>
@@ -1068,10 +1162,28 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Visible invoice không phải full production cost.
-Phân tích theo nguyên lý thiết kế: Visible invoice không phải full production cost.</t>
+- 1.0đ: Vạch trần hiện tượng hóa đơn model $3k chỉ là phần nổi, thiết lập danh mục chi phí toàn diện.
+- 1.0đ: Phân bổ đúng các hạng mục hạ tầng phụ trợ (Vector DB, Tracing storage) độc lập.
+- 1.0đ: Phân lập rạch ròi chi phí lãng phí vận hành (Moderation, retries) tránh tính trùng với hóa đơn chính.
+- 1.0đ: Mô hình hóa chi phí nhân sự con người (80 giờ reviewer $\times$ hourly rate) vào tổng chi phí vận hành.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Danh mục Kiểm kê Toàn diện Chi phí AI Sản xuất (Production AI Cost Inventory) Không Tính trùng lặp (Zero Double-counting):
+1. **Bản chất của Vấn đề Chi phí Ẩn (The Hidden Iceberg of AI Costs)**:
+Hóa đơn thanh toán trực tiếp cho mô hình (Model Invoice) là $3.000 USD/tháng chỉ là phần nổi của tảng băng chìm. Nếu chỉ báo cáo $3.000, doanh nghiệp đang đánh lừa chính mình về bức tranh tài chính thực tế. Cần lập bảng kiểm kê bóc tách theo 4 danh mục chi phí độc lập không chồng lấn.
+2. **Cấu trúc Danh mục Kiểm kê Chi phí Chuẩn mực (Cost Inventory Taxonomy)**:
+| Danh mục Chi phí (Cost Bucket) | Hạng mục Cụ thể | Phương pháp Đo lường &amp; Tránh Tính Trùng (Zero Double-counting) |
+| :--- | :--- | :--- |
+| **1. Trực tiếp Mô hình (Direct Inference API)** | - Lời gọi mô hình thành công (Success API calls) | Trích xuất từ hóa đơn model provider: Chỉ tính các tokens của lượt gọi sinh kết quả nghiệp vụ cuối cùng. |
+| **2. Tài nguyên Hạ tầng Phụ trợ (Supporting Infrastructure)** | - Vector Database SaaS / Cluster&lt;br&gt;- Telemetry &amp; Tracing Ingestion Storage | Chi phí đăng ký cố định hoặc theo dung lượng lưu trữ của Qdrant/Pinecone và Datadog/Tempo. Tách riêng khỏi chi phí mạng thông thường. |
+| **3. Lãng phí &amp; Thử lại Vận hành (Operational Overhead &amp; Retries)** | - Moderation guardrails API&lt;br&gt;- Retry loops do lỗi schema/timeout | **Nguyên tắc chống tính trùng**: Bóc tách riêng số token tiêu tốn cho các lần retry thất bại và moderation ra khỏi Danh mục 1 để đo lường tỷ lệ hao phí (Wasted Spend). |
+| **4. Nhân sự Thẩm định Con người (Human Capital &amp; Review)** | - 80 giờ làm việc của Chuyên gia Reviewer | Tính toán: $\text{Cost} = 80 \text{ giờ} \times \text{Hourly Rate (USD/h)}$. Đây là chi phí nhân công, tuyệt đối không gộp chung vào chi phí phần mềm. |
+3. **Công thức Tổng Hợp Nhất (Fully-loaded Monthly Cost Formula)**:
+$$\text{Total Production Cost} = \text{Cost}_{\text{Model}} + \text{Cost}_{\text{VectorDB}} + \text{Cost}_{\text{Tracing}} + \text{Cost}_{\text{Retries}} + (80 \times \text{Rate}_{\text{Human}})$$
+Giúp ban giám đốc nhìn thấy bức tranh chi phí toàn diện (Fully-loaded TCO) để định giá gói dịch vụ chính xác.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Kiểm kê Chi phí Sản xuất trong FinOps AI (Production AI Cost Inventory &amp; Zero Double-counting): Một sai lầm phổ biến là chỉ nhìn vào hóa đơn OpenAI/Anthropic ($3k) mà bỏ qua chi phí cơ sở dữ liệu vector, chi phí lưu trữ hàng triệu trace log, chi phí các vòng lặp retry lãng phí, và đặc biệt là 80 giờ lương của đội ngũ chuyên gia duyệt bài. Phân loại rạch ròi thành 4 nhóm độc lập bảo đảm tính minh bạch tài chính và cung cấp dữ liệu chính xác cho việc tối ưu hóa chi phí.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation: Managing AI/ML Costs &amp; Google Cloud Architecture Framework: Cost Optimization Pillar</t>
         </is>
       </c>
     </row>
@@ -1154,10 +1266,25 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không chọn cache/self-host chỉ vì cost tổng tăng.
-Phân tích theo nguyên lý thiết kế: Không chọn cache/self-host chỉ vì cost tổng tăng.</t>
+- 1.0đ: Xác định chính xác Dominant Cost Driver là Output Token Inflation (+60% tokens/request).
+- 1.0đ: Phân tích cơ chế kinh tế: giá Output Token đắt gấp 3-4 lần Input Token giải thích mức tăng 40% tổng chi phí.
+- 1.0đ: Loại trừ các nhân tố khác (request +5%, storage +2%, retry giữ nguyên) dựa trên số liệu đề bài.
+- 1.0đ: Thiết kế kế hoạch đo lường tiếp theo (phân vị P90/P99 completion tokens theo feature, audit prompt verbosity).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định Nhân tố Chi phối Chi phí Chính (Dominant Cost Driver Identification):
+- Phân tích biến động các nhân tố:
+  + Số lượng requests: Chỉ tăng nhẹ $+5\%$.
+  + Tỷ lệ retry kỹ thuật: Giữ nguyên không đổi ($0\%$ thay đổi).
+  + Chi phí lưu trữ Storage: Tăng nhẹ $+2\%$.
+  + **Số lượng Token Đầu ra trên mỗi Request (Output Tokens / Request)**: Tăng vọt tới **$+60\%$**.
+- **Kết luận Nhân tố Chi phối (Dominant Driver)**: **Hiện tượng Bùng nổ Token Đầu ra (Output Token Inflation / Verbosity Drift)** chính là nguyên nhân độc tôn dẫn đến mức tăng 40% tổng chi phí của tháng này. Trong cấu trúc giá của các nhà cung cấp LLM (OpenAI/Anthropic), đơn giá Output Token luôn đắt gấp 3 đến 4 lần so với Input Token. Khi mỗi câu trả lời dài thêm 60%, chi phí sinh từ của mô hình tăng phi mã, đè bẹp các biến động nhỏ khác.
+2. Thiết kế Kế hoạch Đo lường Kiểm chứng Kế tiếp (Next Measurement Plan):
+- **Đo lường Phân bổ Độ dài Output theo Phân vị (Token Percentile Distribution)**: Thu thập histogram và đo lường P50, P90, P99 của `completion_tokens` phân rã theo từng `prompt_template` và `feature_name` để khoanh vùng tính năng bị phình độ dài.
+- **Kiểm tra Lịch sử Thay đổi Prompt &amp; Model Params**: Rà soát Git log xem có kỹ sư nào vừa sửa system prompt (thêm yêu cầu 'giải thích chi tiết hơn', 'bổ sung ví dụ'), hoặc thay đổi tham số `max_tokens` / `temperature` khiến mô hình sinh lời dài dòng không cần thiết.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Bản đồ Nhân tố Chi phí trong FinOps AI (Cost Driver Attribution): Khi hóa đơn AI tăng vọt 40%, phản ứng sai lầm là vội vàng đổ lỗi cho lượng truy cập hoặc hạ tầng. Bằng cách bóc tách từng nhân tố toán học ($Cost = Requests \times [Tokens_{in} \times P_{in} + Tokens_{out} \times P_{out}]$), chúng ta xác định ngay thủ phạm là Output Token (+60%). Tập trung đo lường độ dài văn bản sinh ra giúp tiết kiệm hàng nghìn USD mà không cần can thiệp vào kiến trúc phức tạp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation: Cloud Cost Drivers in Machine Learning &amp; OpenAI Pricing Structure Documentation</t>
         </is>
       </c>
     </row>
@@ -1308,10 +1435,30 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nhân traffic chưa đủ; giữ rõ driver nào scale tuyến tính và driver nào theo peak.
-Phân tích theo nguyên lý thiết kế: Nhân traffic chưa đủ; giữ rõ driver nào scale tuyến tính và driver nào theo peak.</t>
+- 1.0đ: Phân tích định lượng so sánh 3 kịch bản: tính đúng tổng token (MVP 12M vs Growth/Campaign 60M).
+- 1.0đ: Phân biệt được nhân tố scale tuyến tính theo ngày (token cost) vs nhân tố scale theo đỉnh tức thời (peak concurrency).
+- 1.0đ: Chỉ ra rủi ro chí mạng của Kịch bản Campaign: nghẽn rate limit 200 req/s trong 2 giờ dù tổng token không tăng.
+- 1.0đ: Xác định chính xác trigger đổi stack và đề xuất giải pháp kiến trúc phù hợp (PTU / Self-hosted vLLM autoscaling).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. So sánh Ba Kịch bản Tải và Nhân tố Thúc đẩy Chi phí (Workload / Cost-Driver Comparison):
+- **Kịch bản 1: MVP (10.000 req/ngày, Peak 20 req/s)**:
+  + *Tổng lượng token*: $10.000 \times 1.200 = 12$ triệu tokens/ngày.
+  + *Đặc tính chi phí*: Chi phí mô hình tính theo token là chính; tải đỉnh 20 req/s nằm hoàn toàn trong hạn ngạch mặc định của Cloud API. Tỷ lệ ca leo thang con người thấp.
+- **Kịch bản 2: Growth (50.000 req/ngày, Peak 60 req/s)**:
+  + *Tổng lượng token*: $50.000 \times 1.200 = 60$ triệu tokens/ngày (tăng gấp 5 lần MVP).
+  + *Đặc tính chi phí*: Chi phí model API tăng tuyến tính theo thể tích; tải đỉnh 60 req/s bắt đầu chạm ngưỡng giới hạn tốc độ (Rate Limit Tier 2). Chi phí nhân sự reviewer tăng tương ứng với số ca lỗi.
+- **Kịch bản 3: Campaign (50.000 req/ngày, Peak 200 req/s tập trung trong 2 giờ)**:
+  + *Tổng lượng token*: Vẫn là 60 triệu tokens/ngày (tổng chi phí token tiêu thụ trong ngày KHÔNG ĐỔI so với Growth).
+  + *Đặc tính chi phí*: Xung đột tải đỉnh cực đoan! 200 req/s trong 2 giờ sẽ làm nổ tung toàn bộ hạn ngạch API thông thường, gây ra bão lỗi HTTP 429 (Rate Limit Exceeded) và hàng đợi nghẽn cục bộ.
+2. Điểm Kích hoạt Chuyển đổi Kiến trúc Hạ tầng (Trigger to Change Stack):
+- **Điểm kích hoạt (Trigger Point)**: Sự xuất hiện của **Tải đỉnh Đột biến 200 req/s trong Kịch bản Campaign**.
+- **Giải pháp Chuyển đổi Kiến trúc Bắt buộc**:
+  + Không thể dùng mô hình API Public chia sẻ thông thường (Public Pay-per-token API).
+  + Bắt buộc phải chuyển đổi sang: **Provisioned Throughput Units (PTU / Reserved Capacity)** từ nhà cung cấp đám mây (Azure/AWS Bedrock),   hoặc **Tự triển khai Cụm GPU Tự lưu trữ (Self-hosted vLLM on Kubernetes)** có cấu hình Auto-scaling để chịu tải 200 req/s mà không bị gián đoạn dịch vụ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Mô hình hóa Tải và Điểm Gãy Hạ tầng (Workload Modeling &amp; Architectural Tipping Points): Một sai lầm của kỹ sư là chỉ nhân tổng số request trong ngày (50k req) để ước tính chi phí. Kịch bản Campaign có cùng thể tích token với Growth, nhưng phân phối thời gian bị dồn nén cực độ (Peak 200 req/s trong 2h). Chi phí token scale theo ngày (Linear Volume), nhưng hạ tầng và giới hạn kết nối lại scale theo giây (Instantaneous Concurrency). Nhận diện tải đỉnh 200 req/s làm trigger chuyển sang hạ tầng chuyên dụng bảo vệ hệ thống không bị sập.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Addressing Cascading Failures &amp; OpenAI Provisioned Throughput Documentation</t>
         </is>
       </c>
     </row>
@@ -1390,10 +1537,26 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi intervention phải nối driver tác động được.
-Phân tích theo nguyên lý thiết kế: Mỗi intervention phải nối driver tác động được.</t>
+- 1.0đ: Xếp Caching vào diện LÀM NGAY (P0) và tính toán mức tiết kiệm tiềm năng (~25% tổng chi phí).
+- 1.0đ: Nhấn mạnh sự chấp thuận của Security (cache mã hóa 10m) làm căn cứ triển khai an toàn.
+- 1.0đ: Xếp Truncate Output vào diện LÀM SAU (P1) vì output token đang ổn định, tránh rủi ro chất lượng.
+- 1.0đ: LOẠI BỎ dứt khoát giải pháp Self-host do chi phí CAPEX khổng lồ và không giải quyết đúng nguyên nhân gốc.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Xếp hạng Ưu tiên Hành động Tối ưu hóa (Làm ngay / Làm sau / Loại bỏ) cho Bài toán Chi phí AI:
+1. **LÀM NGAY (Immediate P0): Triển khai Bộ đệm Lưu trữ Ngữ liệu Mã hóa (Encrypted Retrieval Cache 10m)**:
+- **Căn cứ kỹ thuật vững chắc**:
+  + Báo cáo audit chỉ ra tới **45% tổng chi phí hệ thống bắt nguồn từ các truy vấn retrieval giống hệt nhau lặp đi lặp lại**.
+  + Tỷ lệ đọc trúng cache tiềm năng (cache hit estimate) lên tới **55%**.
+  + Bộ phận An ninh Thông tin (Security) đã chính thức phê duyệt chính sách cho phép cache mã hóa trong 10 phút.
+- **Tác động kinh tế**: Ngay lập tức cắt giảm được: $45\% \times 55\% \approx \mathbf{24.75\%}$ tổng chi phí toàn hệ thống mà không làm suy giảm chất lượng câu trả lời, triển khai nhanh trong 2 ngày bằng Redis Cache.
+2. **LÀM SAU (Later P1): Cắt ngắn Token Đầu ra (Output Truncation)**:
+- **Căn cứ kỹ thuật**: Dữ liệu audit xác nhận 'output token hiện tại đang ở mức ổn định'. Mặc dù cắt ngắn có thể tiết kiệm thêm một phần chi phí nhỏ, nhưng tiềm ẩn rủi ro làm mất thông tin quan trọng hoặc cắt đứt câu trả lời giữa chừng. Chuyển xuống P1 để nghiên cứu tinh chỉnh prompt súc tích sau khi đã thu được món hời lớn từ caching.
+3. **LOẠI BỎ (Disqualify / Avoid P2): Tự Vận hành Cụm Mô hình (Self-host Model on GPU)**:
+- **Căn cứ kỹ thuật**: Đề xuất này bị **LOẠI BỎ HOÀN TOÀN** trong giai đoạn hiện tại. Chi phí chính đang nằm ở khâu lặp retrieval (45%), chứ không phải do đơn giá API model quá đắt. Tự host mô hình đòi hỏi đầu tư hàng chục nghìn USD mua phần cứng GPU (CAPEX), tuyển thêm kỹ sư hạ tầng vận hành, trong khi bài toán lặp truy vấn vẫn tồn tại 100% nếu không có cache. Đây là sự lãng phí tài nguyên và sai lệch hướng giải quyết.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Can thiệp Nối trực tiếp vào Động lực Chi phí (Connecting Intervention directly to the Cost Driver): Một lỗi kinh điển trong kỹ nghệ là 'thấy chi phí tăng liền vội vàng đòi tự host mô hình' (Premature Self-hosting). Nếu 45% chi phí do lặp truy vấn và có thể tiết kiệm 55% bằng cache 10 phút đã được Security cho phép, thì Caching là can thiệp làm ngay (P0) mang lại ROI tức thì. Loại bỏ các giải pháp tốn kém không giải quyết đúng nguyên nhân gốc là phẩm chất của kỹ sư trưởng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation: Rate Reduction vs Usage Reduction &amp; Redis Semantic Caching Architecture</t>
         </is>
       </c>
     </row>
